--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260623.xlsx
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,539,000</t>
+          <t>1,387,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>1,387,000</t>
+          <t>1,539,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
